--- a/informacoes_impressoras/relatorio_contador_impressoras.xlsx
+++ b/informacoes_impressoras/relatorio_contador_impressoras.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H2"/>
+  <dimension ref="A2:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -474,6 +474,920 @@
           <t>C. Final</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.109</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WBQBH6000QJW </t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>426588</v>
+      </c>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>ALMOXARIFADO</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.246</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WBQBH60008CJ </t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>96040</v>
+      </c>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>AMBULATORIO</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.248</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WB07JC10SAMH </t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>313298</v>
+      </c>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>COMPRAS</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.186</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WB07JA10APBV </t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>203741</v>
+      </c>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>DIRETORIA</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>HP ETHERNET MULTI-ENVIRONMENT</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.187</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>CNCRP891R4</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>54816</v>
+      </c>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>KYOCERA Document Solutions Printing System</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.136</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>VG48832068</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>746768</v>
+      </c>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>FATURAMENTO</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>KYOCERA Document Solutions Printing System</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.134</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>VG49451831</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>478624</v>
+      </c>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>KYOCERA Document Solutions Printing System</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.240</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>VG48832217</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>319105</v>
+      </c>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.90</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WBQAJ5000LMK </t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>498546</v>
+      </c>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>CONTASAPAGAR</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.141</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WB07JC10PB4V </t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>177621</v>
+      </c>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>INTEGRACAO</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.86</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WBQBH6000BXT </t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>510707</v>
+      </c>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>LOGISTICA</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.231</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WBQBH700078Z </t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>345121</v>
+      </c>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>MANUTENCAO</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.188</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WBQBH300092V </t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>197671</v>
+      </c>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.247</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WBQBH6000V7L </t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>550513</v>
+      </c>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>PORTARIA1</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.244</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WB07J9106K1E </t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>43932</v>
+      </c>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>PORTARIA2</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.252</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WB07JC10SHNR </t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>153935</v>
+      </c>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>PRODUCAO</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.251</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WB07J9106LLL </t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>359589</v>
+      </c>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.253</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WBQAJ7000BGX </t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>598970</v>
+      </c>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>RHCOLORIDA</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Samsung C4062FX</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.52</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0CAHBJEJA0004PJ </t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>85212</v>
+      </c>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Samsung C4062FX</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.119</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0CAHBJEJ900017V </t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>266991</v>
+      </c>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>SESMT</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Samsung C4062FX</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.145</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0CAHBJEK60009XZ </t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>377486</v>
+      </c>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>POLI01</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>SEGPATRIMONIAL</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>192.168.8.243</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WB07M515VAHR </t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>28675</v>
+      </c>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>POLI05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>192.168.7.100</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WBQBH6000PMH </t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>448531</v>
+      </c>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>POLI05</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>FATURAMENTO</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>192.168.7.101</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WB07M415CPZJ </t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>146460</v>
+      </c>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>POLI05</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>LABORATORIO</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>192.168.7.197</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WBQAJ200020E </t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>212957</v>
+      </c>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>POLI07</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>COMERCIAL</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>192.168.70.31</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WBQBH4000WKH </t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>281784</v>
+      </c>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>POLI07</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>192.168.70.30</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WBQBH60002ME </t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>218026</v>
+      </c>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>POLI08</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>FATURAMENTO</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>192.168.40.31</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WB07JA10APMV </t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>267800</v>
+      </c>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>POLI08</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>FISCAL</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>192.168.40.32</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WB07JA10AJSM </t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>145014</v>
+      </c>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>POLI08</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>LOGISTICA</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Samsung M4080FX</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>192.168.40.30</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088WB07JC10RTBK </t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>204490</v>
+      </c>
+      <c r="H32" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -486,7 +1400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B3"/>
+  <dimension ref="B2:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -499,7 +1413,28 @@
     <row r="3">
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>192.168.8.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>192.168.8.230</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>192.168.7.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>192.168.7.103</t>
         </is>
       </c>
     </row>
